--- a/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
+++ b/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Requires completing a real order (a permanent record on the shared SUT) each run; deferred pending explicit Human + Di authorization and further shipping/payment-step evidence-gathering not performed this task.</t>
+          <t>Real, live investigation this task confirmed the guest path technically reaches Confirm Order identically to the authenticated path (no technical blocker). Deliberately left deferred: closing it would require a SECOND, separate, permanent order via the anonymous path, exceeding this task's 'minimum necessary permanent state creation' principle. Decision required: Human + Di authorization for a second real, permanent order.</t>
         </is>
       </c>
     </row>
@@ -1451,18 +1451,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HUMAN_REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Same reason as REQ-GCO-03: real, permanent order creation deferred pending Human + Di authorization.</t>
+          <t>Closed this task (Deferred-10 closure): the ONE real, permanent order this enhancement creates, using the shared account from REQ-REG-05, chained immediately after that account's own registration/login testcases.</t>
         </is>
       </c>
     </row>
@@ -1484,18 +1492,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DEPENDENCY_BLOCKED</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-02-SAVED-ADDRESS-REUSE</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-02-SAVED-ADDRESS-REUSE</t>
+        </is>
+      </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Depends on REQ-ACO-01 having already been completed at least once for this account (a saved address only exists after a prior checkout).</t>
+          <t>Closed this task: reuses the real saved address created as a side effect of REQ-ACO-01's own Billing Address submission; a second checkout is entered to observe the address-selection control, but never completed (no second order).</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1547,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
@@ -1558,18 +1574,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DEPENDENCY_BLOCKED</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Reaching the Shipping Method step requires progressing past Billing Address with real, complete data; deferred with REQ-ACO-01 (same root cause).</t>
+          <t>Closed this task: real evidence requires a cart containing a physical (non-digital-download) product -- a digital-only cart skips the Shipping Address/Shipping Method steps entirely (real finding, this task). Observed within the same real order-completion execution as REQ-ACO-01 (governing instruction sec. 7: one controlled state transition validating multiple requirements).</t>
         </is>
       </c>
     </row>
@@ -1591,18 +1615,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DEPENDENCY_BLOCKED</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Same root cause as REQ-SHIP-01/REQ-ACO-01.</t>
+          <t>Closed this task: same shared execution as REQ-ACO-01/REQ-SHIP-01.</t>
         </is>
       </c>
     </row>
@@ -1624,18 +1656,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DEPENDENCY_BLOCKED</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Same root cause; also requires reaching Confirm Order.</t>
+          <t>Closed this task. Real finding: on this SUT, Payments.CashOnDelivery itself carries a real $7.00 'Payment method additional fee' (Payments.CheckMoneyOrder carries a real $5.00 fee) -- this matches the original CP01 discovery capture's own real total breakdown (Sub-Total 10.00 + Shipping 0.00 + fee 7.00 + Tax 0.00 = Total 17.00), confirming that discovery order also used Cash On Delivery. No numeric threshold is asserted; only that Total reflects the real, observed fee (see REQ-CONF-02).</t>
         </is>
       </c>
     </row>
@@ -1657,18 +1697,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DEPENDENCY_BLOCKED</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Same root cause as REQ-PAY-01.</t>
+          <t>Closed this task: same shared execution as REQ-ACO-01. Real, live-verified content for Cash On Delivery: "You will pay by COD", zero real input/select/textarea fields.</t>
         </is>
       </c>
     </row>
@@ -1690,18 +1738,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DEPENDENCY_BLOCKED</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Requires a completed real order; same root cause as REQ-ACO-01.</t>
+          <t>Closed this task: real Order Completed page, real order number parsed dynamically (never hard-coded, per SRS sec. 10).</t>
         </is>
       </c>
     </row>
@@ -1723,18 +1779,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DEPENDENCY_BLOCKED</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-ACO-01-AUTHENTICATED-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Same root cause as REQ-CONF-01.</t>
+          <t>Closed this task: computed check (Total == Sub-Total + Shipping + Payment method additional fee + Tax) against the real, live-parsed totals -- never a hard-coded literal.</t>
         </is>
       </c>
     </row>
@@ -1756,18 +1820,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DEPENDENCY_BLOCKED</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-OHIST-01-ORDER-APPEARS-IN-HISTORY</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-OHIST-01-ORDER-APPEARS-IN-HISTORY</t>
+        </is>
+      </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Requires a completed real order to exist; same root cause as REQ-ACO-01.</t>
+          <t>Closed this task: read-only check reusing the one real order from REQ-ACO-01; no new mutation.</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1875,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
@@ -1823,7 +1895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1839,41 +1911,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DEPENDENCY_BLOCKED</t>
+          <t>FUNCTIONAL_AND_PERFORMANCE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FUNCTIONAL_AND_PERFORMANCE</t>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FUNCTIONAL_AUTOMATABLE</t>
+          <t>HUMAN_REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>HUMAN_REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
+++ b/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">

--- a/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
+++ b/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
@@ -1418,18 +1418,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HUMAN_REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+          <t>FUNCTIONAL_AUTOMATABLE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ENH02-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ENH02-PW-TC-REQ-GCO-03-GUEST-CHECKOUT-COMPLETION</t>
+        </is>
+      </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Real, live investigation this task confirmed the guest path technically reaches Confirm Order identically to the authenticated path (no technical blocker). Deliberately left deferred: closing it would require a SECOND, separate, permanent order via the anonymous path, exceeding this task's 'minimum necessary permanent state creation' principle. Decision required: Human + Di authorization for a second real, permanent order.</t>
+          <t>Closed under the Controlled REQ-GCO-03 Post-Freeze Validation (Human + Di authorization, commit after Enhancement-02 frozen baseline 521b155): one real, permanent, genuinely anonymous guest-path order (order number 2387519), supplying the DIRECT SYSTEM EVIDENCE the Approved SRS itself disclosed as missing (Evidence Basis was 'AGENT INFERENCE, bridging from DIRECT SYSTEM EVIDENCE on the authenticated path').</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1925,17 +1933,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HUMAN_REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
+++ b/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">

--- a/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
+++ b/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>

--- a/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
+++ b/testmgmt/generated/MVP2_Requirement_Coverage_Matrix.xlsx
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
